--- a/data/trans_bre/P1428-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1428-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,23</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,54</t>
+          <t>-1,28; 0,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,58</t>
+          <t>-0,34; 1,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,97</t>
+          <t>0,56; 6,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,26</t>
+          <t>-0,1; 2,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,21</t>
+          <t>-2,19; 0,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,06</t>
+          <t>-0,53; 1,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,47</t>
+          <t>0,47; 2,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,41; —</t>
+          <t>-56,08; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 79,58</t>
+          <t>-100,0; 94,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>1,75</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>152,37%</t>
+          <t>157,64%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,0</t>
+          <t>3,31; 6,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 2,32</t>
+          <t>-0,15; 2,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,35</t>
+          <t>-1,11; 1,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 3,12</t>
+          <t>0,29; 3,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>238,86; 2875,53</t>
+          <t>200,6; 2947,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,82; 480,01</t>
+          <t>-24,9; 453,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-69,34; 202,92</t>
+          <t>-67,95; 234,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 579,23</t>
+          <t>3,18; 623,25</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,84</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>195,73%</t>
+          <t>124,09%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,32; 13,46</t>
+          <t>6,05; 12,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 8,8</t>
+          <t>3,4; 8,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 5,4</t>
+          <t>0,1; 5,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 9,12</t>
+          <t>2,4; 6,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,29; 385,83</t>
+          <t>89,48; 363,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>113,6; 809,01</t>
+          <t>108,31; 758,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 196,51</t>
+          <t>0,45; 180,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,76; 619,78</t>
+          <t>45,25; 247,89</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,67</t>
+          <t>10,83</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>136,31%</t>
+          <t>145,76%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,31; 17,02</t>
+          <t>5,88; 17,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 15,75</t>
+          <t>5,86; 15,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,27; 15,63</t>
+          <t>7,26; 15,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 13,73</t>
+          <t>7,51; 13,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,23; 124,78</t>
+          <t>30,24; 125,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,94; 211,31</t>
+          <t>49,11; 220,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>101,5; 454,89</t>
+          <t>109,51; 444,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>73,99; 216,17</t>
+          <t>80,2; 233,15</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43,08</t>
+          <t>19,96</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>411,55%</t>
+          <t>194,23%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,05; 31,32</t>
+          <t>17,91; 31,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,12; 23,24</t>
+          <t>9,35; 22,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,16; 22,81</t>
+          <t>11,98; 23,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,17; 71,09</t>
+          <t>15,74; 23,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>73,03; 172,49</t>
+          <t>70,28; 176,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,22; 183,78</t>
+          <t>47,44; 168,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>113,69; 431,29</t>
+          <t>114,62; 447,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>161,15; 830,75</t>
+          <t>127,24; 285,73</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21,92</t>
+          <t>21,82</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>104,69%</t>
+          <t>104,05%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,56; 32,94</t>
+          <t>17,22; 33,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,61; 28,22</t>
+          <t>11,92; 26,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,22; 16,73</t>
+          <t>3,39; 16,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,59; 26,87</t>
+          <t>16,65; 26,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,76; 112,09</t>
+          <t>43,59; 118,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,34; 151,35</t>
+          <t>41,31; 139,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,27; 133,12</t>
+          <t>17,76; 130,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>67,57; 154,59</t>
+          <t>67,32; 151,63</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14,1</t>
+          <t>9,13</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>280,35%</t>
+          <t>173,83%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,85; 11,96</t>
+          <t>8,87; 12,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,92; 8,63</t>
+          <t>5,94; 8,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,99</t>
+          <t>4,65; 7,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,8; 30,46</t>
+          <t>8,03; 10,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>114,3; 185,56</t>
+          <t>112,27; 182,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>101,08; 188,81</t>
+          <t>101,4; 191,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>112,28; 221,45</t>
+          <t>112,97; 224,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>165,41; 597,11</t>
+          <t>138,57; 214,2</t>
         </is>
       </c>
     </row>
